--- a/data_paper_and_repo_publication/manuscript_outputs/census-9_summary.xlsx
+++ b/data_paper_and_repo_publication/manuscript_outputs/census-9_summary.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/medinaja/GDrive_Science/STRI/STEM_TABLES_FORESTGEO/3_BCI/BCI50ha_StemReconstruction_Rtables/data_paper_and_repo_publication/manuscript_outputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F175D5A-7257-DE48-A3CF-A46DC8E024D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{53431340-E925-CB40-80BC-7A9C46DE5954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="27240" windowHeight="16180" xr2:uid="{2557337E-DD20-3F48-95CF-B13D45CA9E31}"/>
+    <workbookView xWindow="15580" yWindow="660" windowWidth="14660" windowHeight="18980" xr2:uid="{2557337E-DD20-3F48-95CF-B13D45CA9E31}"/>
   </bookViews>
   <sheets>
     <sheet name="census-9_summary" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -939,6 +952,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12785DAB-8FB0-3E4C-9EFB-BDAD8F54B78D}">
   <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
